--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B96C7B-4821-7F43-A67F-B3F58E8A28F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07BAA5A-7954-0F4F-915A-B0C60BEC3EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="680" windowWidth="28860" windowHeight="16520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="540" yWindow="680" windowWidth="28860" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="52">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -414,6 +414,190 @@
   </si>
   <si>
     <t>Pendant</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하급</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>접착제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>중급_접착제]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고급</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>접착제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최고급</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>접착제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>하급 접착제</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>중급 접착제</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">고급 접착제 </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>최고급 접착제</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_basic_glue</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glue</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_intermediate_glue</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_advanced_glue</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_mastery_glue</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -561,7 +745,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -583,6 +767,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -945,7 +1130,73 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="13">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15">
+      <c r="A12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
       <c r="F12" s="1"/>
     </row>
   </sheetData>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07BAA5A-7954-0F4F-915A-B0C60BEC3EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51ED367-9AA1-3345-89A7-348C0B8CB263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="680" windowWidth="28860" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="540" yWindow="1100" windowWidth="13500" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
     <sheet name="Artifact" sheetId="3" r:id="rId2"/>
     <sheet name="InitialItem" sheetId="2" r:id="rId3"/>
+    <sheet name="InventoryTab" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="57">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -598,6 +599,26 @@
   </si>
   <si>
     <t>icon_mastery_glue</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum&lt;InventoryTabType&gt;</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum&lt;ItemType&gt;;key</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryTabType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equipment</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1328,4 +1349,51 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{086B8DAC-B633-AD4E-BA75-289E4BADB1B2}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="22.5" customWidth="1"/>
+    <col min="2" max="2" width="29.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51ED367-9AA1-3345-89A7-348C0B8CB263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6204D56F-CDEB-F74D-81CA-14D1F50CF415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="1100" windowWidth="13500" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="540" yWindow="1100" windowWidth="21820" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -619,6 +619,14 @@
   </si>
   <si>
     <t>Material</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>local_string;[Id][Order]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -739,7 +747,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -762,11 +770,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -789,6 +808,10 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1007,218 +1030,256 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16" style="11" customWidth="1"/>
+    <col min="3" max="3" width="25.5" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16" style="11" customWidth="1"/>
+    <col min="7" max="7" width="23.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1">
+    <row r="2" spans="1:7" ht="15.75" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="E2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15">
+    <row r="3" spans="1:7" ht="15">
       <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9">
+        <v>111</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15">
+    <row r="4" spans="1:7" ht="15">
       <c r="A4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9">
+        <v>222</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15">
+    <row r="5" spans="1:7" ht="15">
       <c r="A5" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9">
+        <v>333</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15">
+    <row r="6" spans="1:7" ht="15">
       <c r="A6" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="14">
+        <v>444</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15">
+    <row r="7" spans="1:7" ht="15">
       <c r="A7" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="14">
+        <v>555</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="14">
+        <v>666</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>39</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="14">
+        <v>777</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="E9" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="14">
+        <v>888</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="E10" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1">
+    <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="14">
+        <v>999</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="E11" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15">
+    <row r="12" spans="1:7" ht="15">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="E12" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>4</v>
       </c>
-      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6204D56F-CDEB-F74D-81CA-14D1F50CF415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205189E8-2B19-254B-BCEB-61298720F386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="1100" windowWidth="21820" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7580" yWindow="1100" windowWidth="21820" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="83">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -627,6 +627,456 @@
   </si>
   <si>
     <t>Description</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>문라이트 베일 파우더</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtifactSkin</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>러브문 글로우 파우더</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마도구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더룸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스킨1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마도구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더룸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스킨2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>artifact_powder_skin01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>artifact_powder_skin02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>더스트 펄</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>파우더 가루</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemTag</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum&lt;ItemTag&gt;</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>리피파이 수제 파우더</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FamiliarRecovery</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayerRecovery</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>플레이어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회복약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가루</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노랑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가루</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>노랑 파우더 가루</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사역마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회복약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ColoredPowder</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_player_recovery01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_familiar_recovery01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_yellow_powder</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_powder</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -785,7 +1235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -812,6 +1262,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1030,17 +1481,19 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="19" style="3" customWidth="1"/>
+    <col min="1" max="1" width="32" style="3" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" customWidth="1"/>
     <col min="3" max="3" width="25.5" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
     <col min="5" max="5" width="16" style="11" customWidth="1"/>
-    <col min="7" max="7" width="23.1640625" customWidth="1"/>
+    <col min="6" max="6" width="17.1640625" style="11" customWidth="1"/>
+    <col min="8" max="8" width="23.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -1056,11 +1509,14 @@
       <c r="E1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
@@ -1076,11 +1532,14 @@
       <c r="E2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15">
+    <row r="3" spans="1:8" ht="15">
       <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
@@ -1096,11 +1555,12 @@
       <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="20"/>
+      <c r="G3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15">
+    <row r="4" spans="1:8" ht="15">
       <c r="A4" s="7" t="s">
         <v>13</v>
       </c>
@@ -1116,11 +1576,12 @@
       <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="20"/>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15">
+    <row r="5" spans="1:8" ht="15">
       <c r="A5" s="7" t="s">
         <v>14</v>
       </c>
@@ -1136,11 +1597,12 @@
       <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="20"/>
+      <c r="G5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15">
+    <row r="6" spans="1:8" ht="15">
       <c r="A6" s="7" t="s">
         <v>15</v>
       </c>
@@ -1156,11 +1618,12 @@
       <c r="E6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="20"/>
+      <c r="G6">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15">
+    <row r="7" spans="1:8" ht="15">
       <c r="A7" s="7" t="s">
         <v>21</v>
       </c>
@@ -1176,11 +1639,12 @@
       <c r="E7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="20"/>
+      <c r="G7">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="7" t="s">
         <v>22</v>
       </c>
@@ -1196,11 +1660,12 @@
       <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="20"/>
+      <c r="G8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>39</v>
       </c>
@@ -1216,11 +1681,12 @@
       <c r="E9" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="17"/>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1">
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="7" t="s">
         <v>40</v>
       </c>
@@ -1236,11 +1702,12 @@
       <c r="E10" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="17"/>
+      <c r="G10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
@@ -1256,11 +1723,12 @@
       <c r="E11" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="17"/>
+      <c r="G11">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15">
+    <row r="12" spans="1:8" ht="15">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
@@ -1276,10 +1744,136 @@
       <c r="E12" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="17"/>
+      <c r="G12">
         <v>4</v>
       </c>
-      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A13" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="14">
+        <v>32323</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="17"/>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A14" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="14">
+        <v>43434</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="17"/>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A15" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="14">
+        <v>54675</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="17"/>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A16" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" s="17"/>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A17" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="17"/>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A18" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205189E8-2B19-254B-BCEB-61298720F386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED34DD4-BDFC-6C44-A3E2-C4FA61154A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7580" yWindow="1100" windowWidth="21820" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="81">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -822,14 +822,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>ItemTag</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>enum&lt;ItemTag&gt;</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>리피파이 수제 파우더</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -888,6 +880,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>]</t>
@@ -1235,7 +1228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1262,7 +1255,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1481,7 +1473,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="32" style="3" customWidth="1"/>
@@ -1489,11 +1481,10 @@
     <col min="3" max="3" width="25.5" customWidth="1"/>
     <col min="4" max="4" width="30.83203125" customWidth="1"/>
     <col min="5" max="5" width="16" style="11" customWidth="1"/>
-    <col min="6" max="6" width="17.1640625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="23.1640625" customWidth="1"/>
+    <col min="7" max="7" width="23.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -1509,14 +1500,11 @@
       <c r="E1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+    <row r="2" spans="1:7" ht="15.75" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
@@ -1532,14 +1520,11 @@
       <c r="E2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15">
+    <row r="3" spans="1:7" ht="15">
       <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
@@ -1555,12 +1540,11 @@
       <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="20"/>
-      <c r="G3">
+      <c r="F3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15">
+    <row r="4" spans="1:7" ht="15">
       <c r="A4" s="7" t="s">
         <v>13</v>
       </c>
@@ -1576,12 +1560,11 @@
       <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="20"/>
-      <c r="G4">
+      <c r="F4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15">
+    <row r="5" spans="1:7" ht="15">
       <c r="A5" s="7" t="s">
         <v>14</v>
       </c>
@@ -1597,12 +1580,11 @@
       <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="G5">
+      <c r="F5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15">
+    <row r="6" spans="1:7" ht="15">
       <c r="A6" s="7" t="s">
         <v>15</v>
       </c>
@@ -1618,12 +1600,11 @@
       <c r="E6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="20"/>
-      <c r="G6">
+      <c r="F6">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15">
+    <row r="7" spans="1:7" ht="15">
       <c r="A7" s="7" t="s">
         <v>21</v>
       </c>
@@ -1639,12 +1620,11 @@
       <c r="E7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="20"/>
-      <c r="G7">
+      <c r="F7">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="7" t="s">
         <v>22</v>
       </c>
@@ -1660,12 +1640,11 @@
       <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="20"/>
-      <c r="G8">
+      <c r="F8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>39</v>
       </c>
@@ -1681,12 +1660,11 @@
       <c r="E9" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="17"/>
-      <c r="G9">
+      <c r="F9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="7" t="s">
         <v>40</v>
       </c>
@@ -1702,12 +1680,11 @@
       <c r="E10" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="17"/>
-      <c r="G10">
+      <c r="F10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1">
+    <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
@@ -1723,12 +1700,11 @@
       <c r="E11" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="17"/>
-      <c r="G11">
+      <c r="F11">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15">
+    <row r="12" spans="1:7" ht="15">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
@@ -1744,13 +1720,12 @@
       <c r="E12" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12">
+      <c r="F12">
         <v>4</v>
       </c>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1">
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="7" t="s">
         <v>62</v>
       </c>
@@ -1766,12 +1741,11 @@
       <c r="E13" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="17"/>
-      <c r="G13">
+      <c r="F13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1">
+    <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="7" t="s">
         <v>63</v>
       </c>
@@ -1787,35 +1761,33 @@
       <c r="E14" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="17"/>
-      <c r="G14">
+      <c r="F14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1">
+    <row r="15" spans="1:7" ht="15.75" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C15" s="14">
         <v>54675</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="F15" s="17"/>
-      <c r="G15">
+        <v>70</v>
+      </c>
+      <c r="F15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1">
+    <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>66</v>
@@ -1824,40 +1796,38 @@
         <v>66</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="F16" s="17"/>
-      <c r="G16">
+        <v>69</v>
+      </c>
+      <c r="F16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="14" t="s">
         <v>74</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>76</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>67</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="F17" s="17"/>
-      <c r="G17">
+        <v>76</v>
+      </c>
+      <c r="F17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>67</v>
@@ -1866,12 +1836,12 @@
         <v>67</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="G18">
+      <c r="F18">
         <v>1</v>
       </c>
     </row>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED34DD4-BDFC-6C44-A3E2-C4FA61154A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22895037-C432-6448-A7C5-DB62AA6EB813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7580" yWindow="1100" windowWidth="21820" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7580" yWindow="1100" windowWidth="21820" windowHeight="16100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="81">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1978,7 +1978,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{086B8DAC-B633-AD4E-BA75-289E4BADB1B2}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="22.5" customWidth="1"/>
@@ -2017,6 +2017,38 @@
         <v>56</v>
       </c>
     </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22895037-C432-6448-A7C5-DB62AA6EB813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FD2E08-AE90-824E-83F8-BA0C43AABC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7580" yWindow="1100" windowWidth="21820" windowHeight="16100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11840" yWindow="680" windowWidth="18460" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="127">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -586,10 +586,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Glue</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>icon_intermediate_glue</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -634,10 +630,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>ArtifactSkin</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>러브문 글로우 파우더</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -826,14 +818,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>FamiliarRecovery</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>PlayerRecovery</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>[</t>
     </r>
@@ -1053,10 +1037,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>ColoredPowder</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>icon_player_recovery01</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1070,6 +1050,759 @@
   </si>
   <si>
     <t>icon_powder</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>실키 클라우드 퍼프</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FamiliarTiredRecovery</t>
+  </si>
+  <si>
+    <t>PlayerHpRecovery</t>
+  </si>
+  <si>
+    <t>FamiliarHpRecovery</t>
+  </si>
+  <si>
+    <t>RefinedMaterial</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quest</t>
+  </si>
+  <si>
+    <t>Ride</t>
+  </si>
+  <si>
+    <t>FamiliarCall</t>
+  </si>
+  <si>
+    <t>Quest</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마도구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스틱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕가게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스킨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>슈가 문 스틱</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>artifact_stick_skin02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사역마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회복약2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>폭신폭신 사역마 쿠션</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사역마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회복약3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>부숭부숭 사역마 목도리</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_familiar_recovery02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_familiar_recovery03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>오로라 파르페</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>미카의 포토카드</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>농땡이 파우더 캐슬</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Meterial</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사역마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지침</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회복약1]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_familiar_tired_recovery01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RefinedMaterial</t>
+  </si>
+  <si>
+    <t>Ride</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜솜가루</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오로라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파르페</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미카</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>포토카드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>농땡이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>캐슬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜뭉치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>씨앗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바삭바삭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꿈뭉치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탈것_솜사탕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>솜솜가루</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>솜뭉치 씨앗</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>바삭바삭 꿈뭉치</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>솜사탕</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_ride_cottom_candy</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_sugar_crystal</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_aurora_parfait</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_photo_card_mika</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_powder_castle</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FamiliarCall</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>페로페로 향수</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>페로페로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>향수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_familiar_call01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_cotton_bottle</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_cotton_seed</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_cotton_powder</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>솜솜 보틀</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜솜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보틀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1473,14 +2206,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="32" style="3" customWidth="1"/>
     <col min="2" max="2" width="17.1640625" customWidth="1"/>
     <col min="3" max="3" width="25.5" customWidth="1"/>
     <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16" style="11" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" style="11" customWidth="1"/>
     <col min="7" max="7" width="23.1640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1492,7 +2225,7 @@
         <v>11</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>0</v>
@@ -1512,7 +2245,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>4</v>
@@ -1646,217 +2379,476 @@
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C9" s="14">
-        <v>777</v>
+        <v>32323</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>48</v>
+        <v>62</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C10" s="14">
-        <v>888</v>
+        <v>43434</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>48</v>
+        <v>63</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="14">
-        <v>999</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="C11" s="14"/>
       <c r="D11" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>48</v>
+        <v>87</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C12" s="14">
-        <v>0</v>
+        <v>777</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="F12">
-        <v>4</v>
-      </c>
-      <c r="G12" s="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C13" s="14">
-        <v>32323</v>
+        <v>888</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="C14" s="14">
-        <v>43434</v>
+        <v>999</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="F14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15">
       <c r="A15" s="7" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C15" s="14">
-        <v>54675</v>
+        <v>0</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="F15">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="7" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1">
       <c r="A18" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A19" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A20" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A21" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F18">
+      <c r="E21" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A22" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A23" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A24" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A25" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A26" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A27" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A28" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A29" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A30" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A31" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F31">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D61CC70E-C5FC-CC4C-B7A4-2DD0D72CDAD8}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="17.5" customWidth="1"/>
+    <col min="1" max="1" width="27.33203125" customWidth="1"/>
     <col min="2" max="2" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1914,6 +2906,30 @@
       </c>
       <c r="B7" s="10" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15">
+      <c r="A8" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15">
+      <c r="A9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15">
+      <c r="A10" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1978,75 +2994,110 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{086B8DAC-B633-AD4E-BA75-289E4BADB1B2}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="22.5" customWidth="1"/>
     <col min="2" max="2" width="29.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="10"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="17" t="s">
-        <v>70</v>
+      <c r="D4" s="10"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="10" t="s">
+        <v>79</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="17" t="s">
-        <v>69</v>
+      <c r="D5" s="10"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:4">
       <c r="A7" s="17" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="17" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FD2E08-AE90-824E-83F8-BA0C43AABC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CB71C5-3C39-7C45-BFAD-CCEBA4C5D099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11840" yWindow="680" windowWidth="18460" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10940" yWindow="680" windowWidth="18460" windowHeight="16100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="127">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -3093,12 +3093,8 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>55</v>
-      </c>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CB71C5-3C39-7C45-BFAD-CCEBA4C5D099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A01EB1-A18F-6148-B7B2-E61367C5B79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10940" yWindow="680" windowWidth="18460" windowHeight="16100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10940" yWindow="680" windowWidth="18460" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="126">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1293,10 +1293,6 @@
   </si>
   <si>
     <t>농땡이 파우더 캐슬</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Meterial</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -2448,8 +2444,8 @@
       <c r="D12" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="17" t="s">
-        <v>97</v>
+      <c r="E12" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -2468,8 +2464,8 @@
       <c r="D13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="17" t="s">
-        <v>97</v>
+      <c r="E13" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="F13">
         <v>2</v>
@@ -2488,8 +2484,8 @@
       <c r="D14" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="17" t="s">
-        <v>97</v>
+      <c r="E14" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="F14">
         <v>3</v>
@@ -2508,8 +2504,8 @@
       <c r="D15" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="17" t="s">
-        <v>97</v>
+      <c r="E15" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="F15">
         <v>4</v>
@@ -2518,7 +2514,7 @@
     </row>
     <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>94</v>
@@ -2527,10 +2523,10 @@
         <v>94</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>97</v>
+        <v>114</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -2538,7 +2534,7 @@
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>95</v>
@@ -2547,10 +2543,10 @@
         <v>95</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>97</v>
+        <v>115</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="F17">
         <v>6</v>
@@ -2558,7 +2554,7 @@
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>96</v>
@@ -2567,10 +2563,10 @@
         <v>96</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>97</v>
+        <v>116</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="F18">
         <v>7</v>
@@ -2589,8 +2585,8 @@
       <c r="D19" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="17" t="s">
-        <v>97</v>
+      <c r="E19" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="F19">
         <v>8</v>
@@ -2678,7 +2674,7 @@
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>76</v>
@@ -2687,7 +2683,7 @@
         <v>76</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>77</v>
@@ -2710,7 +2706,7 @@
         <v>74</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -2718,19 +2714,19 @@
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F26">
         <v>2</v>
@@ -2738,19 +2734,19 @@
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F27">
         <v>3</v>
@@ -2758,19 +2754,19 @@
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F28">
         <v>4</v>
@@ -2778,19 +2774,19 @@
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B29" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="C29" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>113</v>
-      </c>
       <c r="E29" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -2798,19 +2794,19 @@
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1">
       <c r="A30" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B30" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>121</v>
-      </c>
       <c r="E30" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -2818,16 +2814,16 @@
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E31" s="17" t="s">
         <v>84</v>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A01EB1-A18F-6148-B7B2-E61367C5B79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8EE285-1CC3-0044-A9A8-523CA12A6FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10940" yWindow="680" windowWidth="18460" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2444,8 +2444,8 @@
       <c r="D12" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>55</v>
+      <c r="E12" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -2464,8 +2464,8 @@
       <c r="D13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>55</v>
+      <c r="E13" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="F13">
         <v>2</v>
@@ -2484,8 +2484,8 @@
       <c r="D14" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>55</v>
+      <c r="E14" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="F14">
         <v>3</v>
@@ -2504,8 +2504,8 @@
       <c r="D15" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="10" t="s">
-        <v>55</v>
+      <c r="E15" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="F15">
         <v>4</v>
@@ -2525,8 +2525,8 @@
       <c r="D16" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>55</v>
+      <c r="E16" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -2545,8 +2545,8 @@
       <c r="D17" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>55</v>
+      <c r="E17" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="F17">
         <v>6</v>
@@ -2565,8 +2565,8 @@
       <c r="D18" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>55</v>
+      <c r="E18" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="F18">
         <v>7</v>
@@ -2585,8 +2585,8 @@
       <c r="D19" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>55</v>
+      <c r="E19" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="F19">
         <v>8</v>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8EE285-1CC3-0044-A9A8-523CA12A6FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01FC730-F6F7-2644-9CFC-19134FBBD7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10940" yWindow="680" windowWidth="18460" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2444,8 +2444,8 @@
       <c r="D12" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>12</v>
+      <c r="E12" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -2464,8 +2464,8 @@
       <c r="D13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>12</v>
+      <c r="E13" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="F13">
         <v>2</v>
@@ -2484,8 +2484,8 @@
       <c r="D14" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>12</v>
+      <c r="E14" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="F14">
         <v>3</v>
@@ -2504,8 +2504,8 @@
       <c r="D15" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>12</v>
+      <c r="E15" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="F15">
         <v>4</v>
@@ -2525,8 +2525,8 @@
       <c r="D16" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>12</v>
+      <c r="E16" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -2545,8 +2545,8 @@
       <c r="D17" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>12</v>
+      <c r="E17" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="F17">
         <v>6</v>
@@ -2565,8 +2565,8 @@
       <c r="D18" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>12</v>
+      <c r="E18" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="F18">
         <v>7</v>
@@ -2585,8 +2585,8 @@
       <c r="D19" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>12</v>
+      <c r="E19" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="F19">
         <v>8</v>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01FC730-F6F7-2644-9CFC-19134FBBD7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3417C79-EA0A-AD4F-8F76-52F6DCA06017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10940" yWindow="680" windowWidth="18460" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3417C79-EA0A-AD4F-8F76-52F6DCA06017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F9FD1B-30F6-AE49-8464-6905212FECDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10940" yWindow="680" windowWidth="18460" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10940" yWindow="680" windowWidth="18460" windowHeight="16100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="127">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1799,6 +1799,10 @@
       </rPr>
       <t>]</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Matreial</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1957,7 +1961,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1984,6 +1988,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2444,8 +2449,8 @@
       <c r="D12" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>55</v>
+      <c r="E12" s="20" t="s">
+        <v>126</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -2464,8 +2469,8 @@
       <c r="D13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>55</v>
+      <c r="E13" s="20" t="s">
+        <v>126</v>
       </c>
       <c r="F13">
         <v>2</v>
@@ -2484,8 +2489,8 @@
       <c r="D14" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>55</v>
+      <c r="E14" s="20" t="s">
+        <v>126</v>
       </c>
       <c r="F14">
         <v>3</v>
@@ -2504,8 +2509,8 @@
       <c r="D15" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="10" t="s">
-        <v>55</v>
+      <c r="E15" s="20" t="s">
+        <v>126</v>
       </c>
       <c r="F15">
         <v>4</v>
@@ -2525,8 +2530,8 @@
       <c r="D16" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>55</v>
+      <c r="E16" s="20" t="s">
+        <v>126</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -2545,8 +2550,8 @@
       <c r="D17" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>55</v>
+      <c r="E17" s="20" t="s">
+        <v>126</v>
       </c>
       <c r="F17">
         <v>6</v>
@@ -2565,8 +2570,8 @@
       <c r="D18" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>55</v>
+      <c r="E18" s="20" t="s">
+        <v>126</v>
       </c>
       <c r="F18">
         <v>7</v>
@@ -2585,8 +2590,8 @@
       <c r="D19" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>55</v>
+      <c r="E19" s="20" t="s">
+        <v>126</v>
       </c>
       <c r="F19">
         <v>8</v>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F9FD1B-30F6-AE49-8464-6905212FECDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E02EA6F-1537-0C45-AB7C-3B8E78C0B980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10940" yWindow="680" windowWidth="18460" windowHeight="16100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10940" yWindow="680" windowWidth="18460" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -1802,8 +1802,7 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Matreial</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>Material</t>
   </si>
 </sst>
 </file>
@@ -2450,7 +2449,7 @@
         <v>47</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>126</v>
+        <v>55</v>
       </c>
       <c r="F12">
         <v>1</v>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SP\sp-data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E02EA6F-1537-0C45-AB7C-3B8E78C0B980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31ED2D60-118F-46C0-AC65-0602FBE27739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10940" yWindow="680" windowWidth="18460" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="21840" windowHeight="38040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="149">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -814,10 +814,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>리피파이 수제 파우더</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>[</t>
     </r>
@@ -1053,10 +1049,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>실키 클라우드 퍼프</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>FamiliarTiredRecovery</t>
   </si>
   <si>
@@ -1272,10 +1264,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>부숭부숭 사역마 목도리</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>icon_familiar_recovery02</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1284,18 +1272,10 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>오로라 파르페</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>미카의 포토카드</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>농땡이 파우더 캐슬</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>[</t>
     </r>
@@ -1654,18 +1634,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>솜뭉치 씨앗</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>바삭바삭 꿈뭉치</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>솜사탕</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>icon_ride_cottom_candy</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1803,6 +1771,126 @@
   </si>
   <si>
     <t>Material</t>
+  </si>
+  <si>
+    <t>초보 마법소녀 새턴이 「마법소녀 위클리」에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 첫 번째 마도구. 빛나는 토성은 소녀에게 무엇을 보여주게 될까?</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>초보 마법소녀 새턴이 「마법소녀 위클리」에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 두 번째 마도구. 7색의 보석은 소녀에게 어떤 꿈을 꾸게 해줄까?</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>초보 마법소녀 새턴이 「마법소녀 위클리」에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 세 번째 마도구. 날개 달린 버블건은 소녀를 어디로 데려가줄까?</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>「마법소녀 위클리」에서 주문할 수 있는  '소녀의 꿈, 핑크 아티팩트 추가 2종 세트'의 마도구. 무엇이든 갈고, 섞고, 흩뿌려보자!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>「마법소녀 위클리」에서 주문할 수 있는  '소녀의 꿈, 핑크 아티팩트 추가 2종 세트'의 마도구. 작지만 단단한 결정이 오래된 소망을 간직하고 있다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>달빛보다 신비롭고 솜사탕보다 달콤한 마법소녀가 당신의 꿈이었다면!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무도 보지 않는 밤, 문라이트 베일 파우더는 더 밝게 빛을 발한다. 무엇으로든 변하고 싶은 마음은 소녀의 힘에 날개를 달아줄 것이다!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>러브문 글로우 파우더가 마법소녀에게 힘을 더한다. 사랑에 빠진 소녀의 열정을 막을 수 있는 건 아무것도 없지!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>저항할 수 없는 묘한 향기를 풍겨 근처에 있는 사역마를 끌어당기는 미스테리한 향수. 매료된 사역마는 임시 계약을 맺어 하루 동안 당신을 돕는 데에 동의할 것이다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>리피파이가 애정으로 한 알 한 알 손수 뭉친 진주빛 알갱이 펄 파우더. 사역마에게 사용하면 체력을 5 회복시켜준다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>미정</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>실키 퍼프</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>지쳐서 푸석해진 사역마를 순식간에 뽀송하게 되돌려주는 실키 퍼프.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>리피파이의 손길이 구석구석 닿은 파우더 공예품. 본인은 그저 심심풀이로 만든 잡동사니라지만, 놀라운 섬세함이 눈길을 사로잡는다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>리피파이의 파우더리 캐슬</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>보송송 목도리</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>추운 날씨엔 사역마에게 따스한 목도리를 둘러주자. 찬바람에 소모된 체력을 즉시 100 회복할 수 있다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>솜사탕 가게의 숨겨진 메뉴로 미카의 기분이 내킬 때만 맛볼 수 있는 특제 오로라 파르페. 톡톡 튀는 팝핑캔디와 갖가지 캔디시럽이 내키는 대로 뒤섞인 아름다운 카오스가 황홀경을 맛보여준다고.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>미카의 오로라 파르페</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이돌 그룹의 멤버로 활동하던 시절에 소량 제작되었던 미카의 포토카드. 더이상 판매되지 않는 레어템이라 미카의 팬에게는 굉장한 보물일지도?!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>홈베이킹에 쓰이는 가정용 솜사탕 재료. 솜사탕 가게에서 조금씩 얻을 수 있다?</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>달달한 솜이 폭신하게 열린 솜솜 열매. 잘 심어 가꾸면 더 많은 솜사탕 재료를 얻을 수 있을 것이다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>홈베이킹용 솜솜가루가 달빛을 지나치게 흡수해 파랗게 물든 꿈결정. 때로는 실패가 성공보다 더 아름다운 결과를 가져오는 법이다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>솜사타</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>푸른 꿈결정</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>솜솜 열매</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>달콤한 솜사탕을 집에서도 만들고 싶다면 솜솜 보틀이 필요할 것이다. 전용 용기가 솜사탕의 달콤함을 오래도록 지켜줄 테니까!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>솜사타에 올라타! 바람처럼 빠르게 데려다줄거야!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>뽀송 프로그 데오도란트</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>이마에 맺힌 땀방울을 확실하게 잡아주는 뽀송 프로그 데오도란트. 기분 좋은 쿨링 효과가 체력을 50 회복시켜준다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2207,14 +2295,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:G31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="32" style="3" customWidth="1"/>
-    <col min="2" max="2" width="17.1640625" customWidth="1"/>
-    <col min="3" max="3" width="25.5" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" style="11" customWidth="1"/>
-    <col min="7" max="7" width="23.1640625" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" customWidth="1"/>
+    <col min="3" max="3" width="25.42578125" customWidth="1"/>
+    <col min="4" max="4" width="30.85546875" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" style="11" customWidth="1"/>
+    <col min="7" max="7" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1">
@@ -2257,7 +2345,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15">
+    <row r="3" spans="1:7" ht="13.5">
       <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
@@ -2277,15 +2365,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15">
+    <row r="4" spans="1:7" ht="13.5">
       <c r="A4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="9">
-        <v>222</v>
+      <c r="C4" s="9" t="s">
+        <v>119</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>20</v>
@@ -2297,15 +2385,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15">
+    <row r="5" spans="1:7" ht="13.5">
       <c r="A5" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="9">
-        <v>333</v>
+      <c r="C5" s="9" t="s">
+        <v>120</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>19</v>
@@ -2317,15 +2405,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15">
+    <row r="6" spans="1:7" ht="13.5">
       <c r="A6" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="14">
-        <v>444</v>
+      <c r="C6" s="14" t="s">
+        <v>121</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>26</v>
@@ -2337,15 +2425,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15">
+    <row r="7" spans="1:7" ht="13.5">
       <c r="A7" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="14">
-        <v>555</v>
+      <c r="C7" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>25</v>
@@ -2364,8 +2452,8 @@
       <c r="B8" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="14">
-        <v>666</v>
+      <c r="C8" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>27</v>
@@ -2384,8 +2472,8 @@
       <c r="B9" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="14">
-        <v>32323</v>
+      <c r="C9" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>62</v>
@@ -2404,8 +2492,8 @@
       <c r="B10" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="14">
-        <v>43434</v>
+      <c r="C10" s="14" t="s">
+        <v>126</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>63</v>
@@ -2419,14 +2507,16 @@
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="10" t="s">
-        <v>87</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>12</v>
@@ -2469,7 +2559,7 @@
         <v>48</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F13">
         <v>2</v>
@@ -2489,13 +2579,13 @@
         <v>49</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F14">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15">
+    <row r="15" spans="1:7" ht="13.5">
       <c r="A15" s="7" t="s">
         <v>42</v>
       </c>
@@ -2509,7 +2599,7 @@
         <v>50</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F15">
         <v>4</v>
@@ -2518,19 +2608,19 @@
     </row>
     <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -2538,19 +2628,19 @@
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="7" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F17">
         <v>6</v>
@@ -2558,19 +2648,19 @@
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F18">
         <v>7</v>
@@ -2578,7 +2668,7 @@
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1">
       <c r="A19" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>65</v>
@@ -2587,10 +2677,10 @@
         <v>65</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F19">
         <v>8</v>
@@ -2598,19 +2688,19 @@
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -2618,19 +2708,19 @@
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1">
       <c r="A21" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>64</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -2638,19 +2728,19 @@
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B22" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>92</v>
-      </c>
       <c r="E22" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F22">
         <v>2</v>
@@ -2658,19 +2748,19 @@
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1">
       <c r="A23" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>93</v>
-      </c>
       <c r="E23" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F23">
         <v>3</v>
@@ -2678,19 +2768,19 @@
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -2698,19 +2788,19 @@
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -2718,19 +2808,19 @@
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F26">
         <v>2</v>
@@ -2738,19 +2828,19 @@
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F27">
         <v>3</v>
@@ -2758,19 +2848,19 @@
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F28">
         <v>4</v>
@@ -2778,19 +2868,19 @@
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -2798,19 +2888,19 @@
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -2818,19 +2908,19 @@
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -2846,10 +2936,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D61CC70E-C5FC-CC4C-B7A4-2DD0D72CDAD8}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="27.33203125" customWidth="1"/>
-    <col min="2" max="2" width="19.83203125" customWidth="1"/>
+    <col min="1" max="1" width="27.28515625" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2868,7 +2958,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15">
+    <row r="3" spans="1:2" ht="13.5">
       <c r="A3" s="7" t="s">
         <v>13</v>
       </c>
@@ -2876,7 +2966,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15">
+    <row r="4" spans="1:2" ht="13.5">
       <c r="A4" s="7" t="s">
         <v>14</v>
       </c>
@@ -2884,7 +2974,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15">
+    <row r="5" spans="1:2" ht="13.5">
       <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
@@ -2892,7 +2982,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15">
+    <row r="6" spans="1:2" ht="13.5">
       <c r="A6" s="7" t="s">
         <v>21</v>
       </c>
@@ -2900,7 +2990,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15">
+    <row r="7" spans="1:2" ht="13.5">
       <c r="A7" s="7" t="s">
         <v>22</v>
       </c>
@@ -2908,7 +2998,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15">
+    <row r="8" spans="1:2" ht="13.5">
       <c r="A8" s="7" t="s">
         <v>60</v>
       </c>
@@ -2916,7 +3006,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15">
+    <row r="9" spans="1:2" ht="13.5">
       <c r="A9" s="7" t="s">
         <v>61</v>
       </c>
@@ -2924,9 +3014,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15">
+    <row r="10" spans="1:2" ht="13.5">
       <c r="A10" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>34</v>
@@ -2941,9 +3031,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3404EB02-A5A0-8544-AC1C-24A6932127D0}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2962,7 +3052,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15">
+    <row r="3" spans="1:2" ht="13.5">
       <c r="A3" s="7" t="s">
         <v>13</v>
       </c>
@@ -2970,7 +3060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15">
+    <row r="4" spans="1:2" ht="13.5">
       <c r="A4" s="7" t="s">
         <v>14</v>
       </c>
@@ -2978,7 +3068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15">
+    <row r="5" spans="1:2" ht="13.5">
       <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
@@ -2995,10 +3085,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{086B8DAC-B633-AD4E-BA75-289E4BADB1B2}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="22.5" customWidth="1"/>
-    <col min="2" max="2" width="29.83203125" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -3028,7 +3118,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>55</v>
@@ -3037,7 +3127,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>55</v>
@@ -3046,7 +3136,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>55</v>
@@ -3054,7 +3144,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>55</v>
@@ -3070,15 +3160,15 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>55</v>
@@ -3086,7 +3176,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>55</v>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SP\sp-data\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31ED2D60-118F-46C0-AC65-0602FBE27739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC2B11F-85AA-7F40-A72F-5078A87E2155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="21840" windowHeight="38040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6520" yWindow="4620" windowWidth="22880" windowHeight="12580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="153">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1890,6 +1890,43 @@
   </si>
   <si>
     <t>이마에 맺힌 땀방울을 확실하게 잡아주는 뽀송 프로그 데오도란트. 기분 좋은 쿨링 효과가 체력을 50 회복시켜준다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꿈뭉치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>꿈뭉치</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>꿈뭉치 설명</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_dreambundle</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2294,15 +2331,15 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="32" style="3" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" customWidth="1"/>
-    <col min="3" max="3" width="25.42578125" customWidth="1"/>
-    <col min="4" max="4" width="30.85546875" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" style="11" customWidth="1"/>
-    <col min="7" max="7" width="23.140625" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" customWidth="1"/>
+    <col min="3" max="3" width="25.5" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="23.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1">
@@ -2345,7 +2382,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="13.5">
+    <row r="3" spans="1:7" ht="15">
       <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
@@ -2365,7 +2402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="13.5">
+    <row r="4" spans="1:7" ht="15">
       <c r="A4" s="7" t="s">
         <v>13</v>
       </c>
@@ -2385,7 +2422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="13.5">
+    <row r="5" spans="1:7" ht="15">
       <c r="A5" s="7" t="s">
         <v>14</v>
       </c>
@@ -2405,7 +2442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="13.5">
+    <row r="6" spans="1:7" ht="15">
       <c r="A6" s="7" t="s">
         <v>15</v>
       </c>
@@ -2425,7 +2462,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="13.5">
+    <row r="7" spans="1:7" ht="15">
       <c r="A7" s="7" t="s">
         <v>21</v>
       </c>
@@ -2585,7 +2622,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="13.5">
+    <row r="15" spans="1:7" ht="15">
       <c r="A15" s="7" t="s">
         <v>42</v>
       </c>
@@ -2688,39 +2725,39 @@
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>66</v>
+        <v>149</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>76</v>
+        <v>152</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>118</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1">
       <c r="A21" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -2728,79 +2765,79 @@
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>77</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>77</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>75</v>
+        <v>90</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -2808,99 +2845,99 @@
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>94</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>94</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>94</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>95</v>
+        <v>105</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -2908,23 +2945,50 @@
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A32" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A33" s="7"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -2936,10 +3000,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D61CC70E-C5FC-CC4C-B7A4-2DD0D72CDAD8}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="1" max="1" width="27.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2958,7 +3022,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2" ht="15">
       <c r="A3" s="7" t="s">
         <v>13</v>
       </c>
@@ -2966,7 +3030,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2" ht="15">
       <c r="A4" s="7" t="s">
         <v>14</v>
       </c>
@@ -2974,7 +3038,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2" ht="15">
       <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
@@ -2982,7 +3046,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2" ht="15">
       <c r="A6" s="7" t="s">
         <v>21</v>
       </c>
@@ -2990,7 +3054,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2" ht="15">
       <c r="A7" s="7" t="s">
         <v>22</v>
       </c>
@@ -2998,7 +3062,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="13.5">
+    <row r="8" spans="1:2" ht="15">
       <c r="A8" s="7" t="s">
         <v>60</v>
       </c>
@@ -3006,7 +3070,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="13.5">
+    <row r="9" spans="1:2" ht="15">
       <c r="A9" s="7" t="s">
         <v>61</v>
       </c>
@@ -3014,7 +3078,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
+    <row r="10" spans="1:2" ht="15">
       <c r="A10" s="7" t="s">
         <v>83</v>
       </c>
@@ -3031,9 +3095,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3404EB02-A5A0-8544-AC1C-24A6932127D0}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3052,7 +3116,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2" ht="15">
       <c r="A3" s="7" t="s">
         <v>13</v>
       </c>
@@ -3060,7 +3124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2" ht="15">
       <c r="A4" s="7" t="s">
         <v>14</v>
       </c>
@@ -3068,7 +3132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2" ht="15">
       <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
@@ -3085,10 +3149,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{086B8DAC-B633-AD4E-BA75-289E4BADB1B2}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+    <col min="1" max="1" width="22.5" customWidth="1"/>
+    <col min="2" max="2" width="29.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hansu/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC2B11F-85AA-7F40-A72F-5078A87E2155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4467937A-8EE1-AA47-9988-D168ACB58D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6520" yWindow="4620" windowWidth="22880" windowHeight="12580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1911,6 +1911,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>]</t>
@@ -2570,7 +2571,7 @@
         <v>43</v>
       </c>
       <c r="C12" s="14">
-        <v>777</v>
+        <v>1</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>47</v>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hansu/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4467937A-8EE1-AA47-9988-D168ACB58D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BBB836-4E62-1248-AF2E-67EBB855005F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6520" yWindow="4620" windowWidth="22880" windowHeight="12580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="160">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -43,10 +43,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>솔라리</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>icon_solari</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -247,18 +243,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>스틱</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>파우더</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>버블건</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>artifact_powder</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -566,22 +550,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>하급 접착제</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>중급 접착제</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">고급 접착제 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>최고급 접착제</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>icon_basic_glue</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -810,10 +778,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>파우더 가루</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>[</t>
     </r>
@@ -975,10 +939,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>노랑 파우더 가루</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>[</t>
     </r>
@@ -1214,10 +1174,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>폭신폭신 사역마 쿠션</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>[</t>
     </r>
@@ -1813,14 +1769,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>미정</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>실키 퍼프</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>지쳐서 푸석해진 사역마를 순식간에 뽀송하게 되돌려주는 실키 퍼프.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1923,11 +1871,88 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>꿈뭉치 설명</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>icon_dreambundle</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>미니 끈적이 용액</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>포켓 끈적이 용액</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>점보 끈적이 용액</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>고급 끈적이 용액</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬라임으로 만들어진 귀여운 용량의 끈적이 용액. 이 정도라도 얻을 수 있어 다행이다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬라임으로 만들어진 작은 용량의 끈적이 용액. 접착제가 필요할 때 요긴하게 쓰일 수 있을 것이다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬라임으로 만들어진 충분한 용량의 끈적이 용액. 접착제 용도로 사용할 수 있다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>고르고 고른 슬라임만으로 뽑아낸 끈적이 용액. 보통 접착제가 '그냥 붙는다'면, 이것은 '티 안 나게 붙는다' 붙인 티가 나지 않는 점이 예술 그 자체.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>옐로우 허니 파우더</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>정오의 햇살이 가장 진하게 고이는 한때를 곱게 빻아 담았다고 하는 노란빛깔의 파우더. 매듭을 풀면 온기가 새어나와 손끝이 먼저 따뜻해진다. 주머니에 매달린 태그에는 흐린 글씨로 '해가 지기 전에 쓸 것'이라 적혀 있지만, 잘 지켜지지 않는다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>핑크 슈가 파우더</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>새벽하늘이 잠깐 분홍으로 물드는 그 몇 분을 곱게 빻아 담은 고운 입자의 분홍빛깔의 파우더. 주머니에 매달린 태그에는 흐린 글씨로 '3분의 2만 쓸 것'이라 적혀 있지만, 남은 3분의 1의 쓰임을 아는 사람은 아직 없다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>성실한 솜사탕 베이킹 끝에 얻을 수 있는 작고 신비로운 결정. 달콤한 것을 먹고 행복해진 손님들의 감정이 흘러들어와 마법으로 뭉쳐진 것이라는 설이 있다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>꿈꾸는 별의 스틱</t>
+  </si>
+  <si>
+    <t>꿈꾸는 7색 보석 파우더</t>
+  </si>
+  <si>
+    <t>꿈꾸는 윙 버블건</t>
+  </si>
+  <si>
+    <t>해가 가장 높이 뜬 정오, 대장장이가 화로에 태양의 기운을 받아 두드려 낸 쇠 동전. 모든 거래의 기준이 되는 화폐로 사용된다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>솔라</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>사역마 플러피 쿠션</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 같은 포근함으로 어떤 성실한 사역마도 잠들게 만드는 쿠션. 잠든 사역마는 달콤한 꿈을 꾸며 체력을 100 회복한다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>사역마용 실키 퍼프</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2337,7 +2362,7 @@
   <cols>
     <col min="1" max="1" width="32" style="3" customWidth="1"/>
     <col min="2" max="2" width="17.1640625" customWidth="1"/>
-    <col min="3" max="3" width="25.5" customWidth="1"/>
+    <col min="3" max="3" width="87" customWidth="1"/>
     <col min="4" max="4" width="30.83203125" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="11" customWidth="1"/>
     <col min="7" max="7" width="23.1640625" customWidth="1"/>
@@ -2348,19 +2373,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1">
@@ -2371,33 +2396,33 @@
         <v>3</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15">
       <c r="A3" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="9">
-        <v>111</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>6</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -2405,19 +2430,19 @@
     </row>
     <row r="4" spans="1:7" ht="15">
       <c r="A4" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>20</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -2425,19 +2450,19 @@
     </row>
     <row r="5" spans="1:7" ht="15">
       <c r="A5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>17</v>
+        <v>153</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -2445,19 +2470,19 @@
     </row>
     <row r="6" spans="1:7" ht="15">
       <c r="A6" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -2465,19 +2490,19 @@
     </row>
     <row r="7" spans="1:7" ht="15">
       <c r="A7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>25</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7">
         <v>4</v>
@@ -2485,19 +2510,19 @@
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2505,19 +2530,19 @@
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9">
         <v>6</v>
@@ -2525,19 +2550,19 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10">
         <v>7</v>
@@ -2545,19 +2570,19 @@
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11">
         <v>8</v>
@@ -2565,19 +2590,19 @@
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="14">
-        <v>1</v>
-      </c>
-      <c r="D12" s="10" t="s">
+      <c r="E12" s="20" t="s">
         <v>47</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>55</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -2585,19 +2610,19 @@
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="14">
-        <v>888</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>48</v>
-      </c>
       <c r="E13" s="20" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F13">
         <v>2</v>
@@ -2605,19 +2630,19 @@
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="14">
-        <v>999</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>49</v>
-      </c>
       <c r="E14" s="20" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F14">
         <v>3</v>
@@ -2625,19 +2650,19 @@
     </row>
     <row r="15" spans="1:7" ht="15">
       <c r="A15" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="14">
-        <v>0</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>50</v>
-      </c>
       <c r="E15" s="20" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F15">
         <v>4</v>
@@ -2646,19 +2671,19 @@
     </row>
     <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -2666,19 +2691,19 @@
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="7" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="D17" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="20" t="s">
         <v>107</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>118</v>
       </c>
       <c r="F17">
         <v>6</v>
@@ -2686,19 +2711,19 @@
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F18">
         <v>7</v>
@@ -2706,19 +2731,19 @@
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1">
       <c r="A19" s="7" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>65</v>
+        <v>149</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F19">
         <v>8</v>
@@ -2726,19 +2751,19 @@
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="C20" s="14" t="s">
         <v>151</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F20">
         <v>9</v>
@@ -2746,19 +2771,19 @@
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1">
       <c r="A21" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>66</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -2766,19 +2791,19 @@
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -2786,19 +2811,19 @@
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>87</v>
+        <v>157</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>87</v>
+        <v>158</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F23">
         <v>2</v>
@@ -2806,19 +2831,19 @@
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F24">
         <v>3</v>
@@ -2826,19 +2851,19 @@
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -2846,19 +2871,19 @@
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>69</v>
+        <v>147</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2866,19 +2891,19 @@
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="F27">
         <v>2</v>
@@ -2886,19 +2911,19 @@
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="F28">
         <v>3</v>
@@ -2906,19 +2931,19 @@
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="F29">
         <v>4</v>
@@ -2926,19 +2951,19 @@
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -2946,19 +2971,19 @@
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -2966,19 +2991,19 @@
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -3012,7 +3037,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3020,71 +3045,71 @@
         <v>2</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15">
       <c r="A3" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15">
       <c r="A4" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15">
       <c r="A5" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15">
       <c r="A6" s="7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15">
       <c r="A7" s="7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15">
       <c r="A8" s="7" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15">
       <c r="A9" s="7" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15">
       <c r="A10" s="7" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3106,20 +3131,20 @@
         <v>1</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="15" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15">
       <c r="A3" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -3127,7 +3152,7 @@
     </row>
     <row r="4" spans="1:2" ht="15">
       <c r="A4" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -3135,7 +3160,7 @@
     </row>
     <row r="5" spans="1:2" ht="15">
       <c r="A5" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3158,93 +3183,93 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="10" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D3" s="10"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="10" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D4" s="10"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="10" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D5" s="10"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="10" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="17" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="17" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="10" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="10" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="10" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:4">
